--- a/project/outputs_xlsx_solution/prog-loop.4-wide-NF-1.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.4-wide-NF-1.xlsx
@@ -98,6 +98,9 @@
     <t>bne X1, X0, 12</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>[Legend]</t>
   </si>
   <si>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
-  </si>
-  <si>
-    <t>FU Stall</t>
   </si>
   <si>
     <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
@@ -609,9 +609,6 @@
       <c r="AK1">
         <v>34</v>
       </c>
-      <c r="AL1">
-        <v>35</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -890,10 +887,10 @@
         <v>6</v>
       </c>
       <c r="P12" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R12" t="s">
         <v>11</v>
@@ -909,16 +906,16 @@
       <c r="C13" t="s">
         <v>12</v>
       </c>
+      <c r="Q13" t="s">
+        <v>5</v>
+      </c>
       <c r="R13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="s">
-        <v>8</v>
-      </c>
-      <c r="U13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -932,11 +929,14 @@
       <c r="C14" t="s">
         <v>13</v>
       </c>
+      <c r="R14" t="s">
+        <v>5</v>
+      </c>
       <c r="S14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U14" t="s">
         <v>8</v>
@@ -948,9 +948,6 @@
         <v>8</v>
       </c>
       <c r="X14" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" t="s">
         <v>11</v>
       </c>
     </row>
@@ -964,19 +961,19 @@
       <c r="C15" t="s">
         <v>14</v>
       </c>
+      <c r="S15" t="s">
+        <v>5</v>
+      </c>
       <c r="T15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V15" t="s">
-        <v>8</v>
-      </c>
-      <c r="W15" t="s">
         <v>10</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="X15" t="s">
         <v>11</v>
       </c>
     </row>
@@ -990,15 +987,18 @@
       <c r="C16" t="s">
         <v>15</v>
       </c>
+      <c r="T16" t="s">
+        <v>5</v>
+      </c>
       <c r="U16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16" t="s">
-        <v>6</v>
-      </c>
-      <c r="W16" t="s">
         <v>17</v>
       </c>
+      <c r="X16" t="s">
+        <v>8</v>
+      </c>
       <c r="Y16" t="s">
         <v>8</v>
       </c>
@@ -1006,9 +1006,6 @@
         <v>8</v>
       </c>
       <c r="AA16" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB16" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1022,19 +1019,19 @@
       <c r="C17" t="s">
         <v>16</v>
       </c>
+      <c r="U17" t="s">
+        <v>5</v>
+      </c>
       <c r="V17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17" t="s">
-        <v>6</v>
-      </c>
-      <c r="X17" t="s">
         <v>17</v>
       </c>
+      <c r="AA17" t="s">
+        <v>8</v>
+      </c>
       <c r="AB17" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC17" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1048,19 +1045,19 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
+      <c r="V18" t="s">
+        <v>5</v>
+      </c>
       <c r="W18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z18" t="s">
         <v>10</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AB18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1074,19 +1071,19 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
+      <c r="W19" t="s">
+        <v>5</v>
+      </c>
       <c r="X19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA19" t="s">
         <v>10</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AB19" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1100,19 +1097,19 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
+      <c r="X20" t="s">
+        <v>5</v>
+      </c>
       <c r="Y20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AB20" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC20" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1126,19 +1123,19 @@
       <c r="C21" t="s">
         <v>12</v>
       </c>
+      <c r="Y21" t="s">
+        <v>5</v>
+      </c>
       <c r="Z21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AB21" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1152,14 +1149,17 @@
       <c r="C22" t="s">
         <v>13</v>
       </c>
+      <c r="Z22" t="s">
+        <v>5</v>
+      </c>
       <c r="AA22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AC22" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="s">
         <v>8</v>
@@ -1171,9 +1171,6 @@
         <v>8</v>
       </c>
       <c r="AG22" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH22" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1187,19 +1184,19 @@
       <c r="C23" t="s">
         <v>14</v>
       </c>
+      <c r="AA23" t="s">
+        <v>5</v>
+      </c>
       <c r="AB23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE23" t="s">
         <v>10</v>
       </c>
-      <c r="AH23" t="s">
+      <c r="AG23" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1213,15 +1210,18 @@
       <c r="C24" t="s">
         <v>15</v>
       </c>
+      <c r="AB24" t="s">
+        <v>5</v>
+      </c>
       <c r="AC24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE24" t="s">
         <v>17</v>
       </c>
+      <c r="AG24" t="s">
+        <v>8</v>
+      </c>
       <c r="AH24" t="s">
         <v>8</v>
       </c>
@@ -1229,9 +1229,6 @@
         <v>8</v>
       </c>
       <c r="AJ24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1245,19 +1242,19 @@
       <c r="C25" t="s">
         <v>16</v>
       </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AD25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF25" t="s">
         <v>17</v>
       </c>
+      <c r="AJ25" t="s">
+        <v>8</v>
+      </c>
       <c r="AK25" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL25" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1271,19 +1268,19 @@
       <c r="C26" t="s">
         <v>18</v>
       </c>
+      <c r="AD26" t="s">
+        <v>5</v>
+      </c>
       <c r="AE26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH26" t="s">
         <v>10</v>
       </c>
-      <c r="AL26" t="s">
+      <c r="AK26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1297,19 +1294,19 @@
       <c r="C27" t="s">
         <v>19</v>
       </c>
+      <c r="AE27" t="s">
+        <v>5</v>
+      </c>
       <c r="AF27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH27" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI27" t="s">
         <v>10</v>
       </c>
-      <c r="AL27" t="s">
+      <c r="AK27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1323,28 +1320,25 @@
       <c r="C28" t="s">
         <v>20</v>
       </c>
+      <c r="AF28" t="s">
+        <v>5</v>
+      </c>
       <c r="AG28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL28" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1352,7 +1346,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -1360,7 +1354,7 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -1368,7 +1362,7 @@
         <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -1376,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -1384,7 +1378,7 @@
         <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -1392,36 +1386,36 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
         <v>35</v>
